--- a/output/pdf_financials_xlsx/LIFT.xlsx
+++ b/output/pdf_financials_xlsx/LIFT.xlsx
@@ -2719,16 +2719,16 @@
         <v>0.011316</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.005092</v>
+        <v>0.005</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.547</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.938</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.776</v>
       </c>
     </row>
     <row r="93">
@@ -3273,19 +3273,19 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.2324</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-3.385</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-36.187</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-22.516</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-17.741</v>
       </c>
     </row>
     <row r="119">
@@ -4479,7 +4479,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -6226,7 +6230,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -9994,7 +10002,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -12115,7 +12127,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E212" s="5" t="n">
         <v>-1.2324</v>
       </c>

--- a/output/pdf_financials_xlsx/LIFT.xlsx
+++ b/output/pdf_financials_xlsx/LIFT.xlsx
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.156419</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>5.442</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.156419</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>5.442</v>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.156419</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.016</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">

--- a/output/pdf_financials_xlsx/LIFT.xlsx
+++ b/output/pdf_financials_xlsx/LIFT.xlsx
@@ -2091,16 +2091,16 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.331</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.334</v>
       </c>
     </row>
     <row r="65">
@@ -2160,13 +2160,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.907</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.796</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.892</v>
       </c>
     </row>
     <row r="68">
@@ -9766,7 +9766,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
